--- a/data/Studio_Press_1404_2.xlsx
+++ b/data/Studio_Press_1404_2.xlsx
@@ -571,12 +571,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
+          <t>علیرضائی</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
           <t>بشک</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>علیرضائی</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -686,12 +686,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
+          <t>علیرضائی</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
           <t>بشک</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>علیرضائی</t>
         </is>
       </c>
     </row>
@@ -708,12 +708,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>شریفی</t>
+          <t>هاشمی</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>هاشمی</t>
+          <t>رودی</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>رودی</t>
+          <t>شریفی</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
